--- a/outputs/q3/q3_relay_resource_timeline.xlsx
+++ b/outputs/q3/q3_relay_resource_timeline.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实体与组件" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'实体与组件'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'实体与组件'!$A$1:$J$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -511,29 +511,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R-COMP-01</t>
+          <t>R-COMP-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>81.00344048954707</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2504.206487773799</v>
+        <v>2503.956487773799</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2804.206487773799</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.802344286540321</v>
+        <v>0.8006049115403211</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2504.206487773799</v>
+        <v>2503.956487773799</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3261.158915271382</v>
+        <v>3263.170102771382</v>
       </c>
     </row>
     <row r="3">
@@ -549,29 +549,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R-COMP-02</t>
+          <t>R-COMP-05</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4172.397987116188</v>
+        <v>4124.868987116189</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4472.397987116188</v>
+        <v>4424.868987116189</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6420442482456661</v>
+        <v>0.6463111406067772</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4172.397987116188</v>
+        <v>4124.868987116189</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5137.740464396822</v>
+        <v>5084.664504327378</v>
       </c>
     </row>
     <row r="4">
@@ -591,25 +591,25 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5721.741911727985</v>
+        <v>6110.943898832808</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6021.741911727985</v>
+        <v>6410.943898832808</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7567953565433048</v>
+        <v>0.7109232103375329</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5721.741911727985</v>
+        <v>6110.943898832808</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6537.907948221689</v>
+        <v>6986.743725394015</v>
       </c>
     </row>
     <row r="5">
@@ -629,67 +629,29 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4479.752893111123</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7314.782356990602</v>
+        <v>6975.244356990602</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7614.782356990602</v>
+        <v>7275.244356990602</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7600594889337923</v>
+        <v>0.7957114246976813</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>7314.782356990602</v>
+        <v>6975.244356990602</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8126.705021376672</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R-COMP-05</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>6145.052240382385</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>7321.108589166768</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>7621.108589166768</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.9137874815163642</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>7321.108589166768</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>7864.247455613673</v>
+        <v>7740.819504883616</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>